--- a/data/trans_camb/P23_R2-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P23_R2-Habitat-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-11,36; -0,98</t>
+          <t>-11,58; -1,58</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-11,23; -0,73</t>
+          <t>-11,5; -0,98</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-21,13; -10,38</t>
+          <t>-20,66; -9,92</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-4,81; 4,3</t>
+          <t>-4,48; 4,98</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-2,54; 6,16</t>
+          <t>-2,29; 6,68</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-9,19; -1,0</t>
+          <t>-8,9; -0,94</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-6,71; 0,18</t>
+          <t>-6,9; 0,44</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-5,53; 1,67</t>
+          <t>-5,92; 1,48</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-13,69; -7,31</t>
+          <t>-13,54; -6,94</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-24,64; -2,51</t>
+          <t>-25,58; -3,96</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-24,82; -1,95</t>
+          <t>-24,71; -1,89</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-45,5; -25,0</t>
+          <t>-44,96; -24,29</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-19,29; 20,34</t>
+          <t>-17,49; 23,98</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-10,4; 28,56</t>
+          <t>-9,79; 31,59</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-36,21; -5,04</t>
+          <t>-35,5; -4,13</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-19,42; 0,74</t>
+          <t>-19,25; 1,47</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-15,86; 5,12</t>
+          <t>-17,16; 4,59</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-39,4; -23,01</t>
+          <t>-38,8; -21,72</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-7,5; 1,98</t>
+          <t>-7,3; 1,34</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-11,8; -2,49</t>
+          <t>-11,75; -3,08</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-30,22; -13,45</t>
+          <t>-31,22; -13,37</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,21; 9,24</t>
+          <t>0,89; 9,06</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,53; 7,26</t>
+          <t>-0,61; 7,15</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-7,76; -0,42</t>
+          <t>-7,7; -0,36</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-1,97; 4,34</t>
+          <t>-1,77; 4,41</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-4,85; 1,07</t>
+          <t>-5,14; 0,79</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-18,34; -8,52</t>
+          <t>-18,52; -8,24</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-17,38; 5,19</t>
+          <t>-17,05; 3,43</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-27,67; -6,3</t>
+          <t>-27,38; -7,5</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-72,73; -34,14</t>
+          <t>-78,44; -34,2</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,42; 43,85</t>
+          <t>3,4; 42,98</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-2,18; 34,81</t>
+          <t>-2,35; 34,42</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-30,88; -2,0</t>
+          <t>-31,07; -1,62</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-5,8; 14,29</t>
+          <t>-5,94; 14,74</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-14,9; 3,61</t>
+          <t>-15,78; 2,6</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-56,28; -27,66</t>
+          <t>-58,12; -27,19</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-4,39; 6,06</t>
+          <t>-4,06; 6,08</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,72; 9,9</t>
+          <t>-0,71; 9,81</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-13,14; -1,55</t>
+          <t>-13,24; -1,92</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,06; 9,41</t>
+          <t>0,24; 9,31</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,29; 9,72</t>
+          <t>0,49; 9,55</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-16,42; -0,23</t>
+          <t>-17,34; -0,99</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-0,69; 6,33</t>
+          <t>-0,79; 6,2</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,0; 8,14</t>
+          <t>1,02; 8,09</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-16,23; -3,69</t>
+          <t>-15,95; -3,68</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-11,13; 18,01</t>
+          <t>-10,54; 18,21</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-1,77; 29,94</t>
+          <t>-1,82; 28,89</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-34,06; -3,93</t>
+          <t>-33,82; -4,72</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-0,44; 44,3</t>
+          <t>0,81; 41,73</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1,08; 44,51</t>
+          <t>1,24; 42,86</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-62,7; -1,81</t>
+          <t>-66,3; -4,57</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-2,12; 22,83</t>
+          <t>-2,48; 21,98</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>3,3; 29,23</t>
+          <t>3,21; 28,54</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-52,86; -12,85</t>
+          <t>-52,45; -12,79</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-7,97; 0,87</t>
+          <t>-8,1; 0,88</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-14,05; -5,24</t>
+          <t>-13,6; -5,1</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-20,29; -11,38</t>
+          <t>-20,53; -12,33</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-3,64; 4,0</t>
+          <t>-3,9; 4,01</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-6,79; 1,06</t>
+          <t>-7,09; 1,37</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-14,26; -6,23</t>
+          <t>-15,06; -6,42</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-4,87; 1,24</t>
+          <t>-4,68; 1,14</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-8,91; -2,89</t>
+          <t>-8,81; -3,09</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-15,97; -10,23</t>
+          <t>-16,24; -10,07</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-19,37; 2,34</t>
+          <t>-19,45; 2,36</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-33,54; -13,97</t>
+          <t>-32,84; -13,63</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-48,62; -30,46</t>
+          <t>-49,46; -32,16</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-12,51; 15,72</t>
+          <t>-13,18; 15,91</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-22,71; 4,1</t>
+          <t>-23,72; 5,28</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-49,19; -24,76</t>
+          <t>-51,13; -24,59</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-13,94; 3,89</t>
+          <t>-13,58; 3,55</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-25,78; -9,21</t>
+          <t>-25,45; -9,47</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-46,81; -31,63</t>
+          <t>-47,18; -31,45</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-5,24; -0,41</t>
+          <t>-5,63; -0,73</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-7,42; -2,75</t>
+          <t>-7,55; -2,72</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-20,87; -12,54</t>
+          <t>-21,58; -12,99</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,31; 4,62</t>
+          <t>0,3; 4,59</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,55; 3,6</t>
+          <t>-0,64; 3,64</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-10,15; -4,56</t>
+          <t>-10,26; -4,42</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-2,01; 1,38</t>
+          <t>-1,8; 1,34</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-3,55; -0,25</t>
+          <t>-3,34; -0,16</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-14,02; -9,13</t>
+          <t>-14,18; -9,24</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-12,72; -1,18</t>
+          <t>-13,55; -1,86</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-17,95; -7,1</t>
+          <t>-18,27; -7,06</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-52,11; -32,38</t>
+          <t>-53,17; -33,01</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1,15; 19,73</t>
+          <t>1,3; 19,98</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-1,87; 15,5</t>
+          <t>-2,5; 15,3</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-40,53; -19,35</t>
+          <t>-40,45; -18,68</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-6,13; 4,46</t>
+          <t>-5,51; 4,3</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-10,88; -0,86</t>
+          <t>-10,13; -0,49</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-43,5; -29,02</t>
+          <t>-43,95; -29,2</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P23_R2-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P23_R2-Habitat-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-15,33</t>
+          <t>-15,41</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-4,98</t>
+          <t>-5,39</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-10,35</t>
+          <t>-10,6</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-11,58; -1,58</t>
+          <t>-11,78; -0,85</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-11,5; -0,98</t>
+          <t>-11,56; -1,22</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-20,66; -9,92</t>
+          <t>-20,75; -9,91</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-4,48; 4,98</t>
+          <t>-4,57; 4,89</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-2,29; 6,68</t>
+          <t>-2,28; 7,04</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-8,9; -0,94</t>
+          <t>-9,2; -1,49</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-6,9; 0,44</t>
+          <t>-6,58; 0,45</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-5,92; 1,48</t>
+          <t>-5,54; 1,72</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-13,54; -6,94</t>
+          <t>-14,0; -7,17</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-35,33%</t>
+          <t>-35,53%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-21,55%</t>
+          <t>-23,34%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-31,09%</t>
+          <t>-31,85%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-25,58; -3,96</t>
+          <t>-25,14; -1,86</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-24,71; -1,89</t>
+          <t>-24,82; -3,01</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-44,96; -24,29</t>
+          <t>-45,07; -24,55</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-17,49; 23,98</t>
+          <t>-18,12; 24,1</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-9,79; 31,59</t>
+          <t>-9,42; 33,78</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-35,5; -4,13</t>
+          <t>-36,27; -7,44</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-19,25; 1,47</t>
+          <t>-18,88; 1,41</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-17,16; 4,59</t>
+          <t>-15,65; 5,55</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-38,8; -21,72</t>
+          <t>-39,86; -23,2</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-20,14</t>
+          <t>-15,78</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-4,14</t>
+          <t>-4,65</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-12,04</t>
+          <t>-10,21</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-7,3; 1,34</t>
+          <t>-7,58; 1,48</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-11,75; -3,08</t>
+          <t>-11,68; -3,02</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-31,22; -13,37</t>
+          <t>-20,32; -11,39</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,89; 9,06</t>
+          <t>0,96; 9,23</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,61; 7,15</t>
+          <t>-0,88; 7,16</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-7,7; -0,36</t>
+          <t>-7,95; -1,08</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-1,77; 4,41</t>
+          <t>-1,79; 4,45</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-5,14; 0,79</t>
+          <t>-5,25; 0,65</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-18,52; -8,24</t>
+          <t>-13,17; -7,48</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-50,22%</t>
+          <t>-39,34%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-18,04%</t>
+          <t>-20,27%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-38,24%</t>
+          <t>-32,43%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-17,05; 3,43</t>
+          <t>-17,84; 4,03</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-27,38; -7,5</t>
+          <t>-27,55; -8,25</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-78,44; -34,2</t>
+          <t>-48,79; -30,06</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3,4; 42,98</t>
+          <t>3,85; 43,23</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-2,35; 34,42</t>
+          <t>-3,44; 34,21</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-31,07; -1,62</t>
+          <t>-32,18; -4,65</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-5,94; 14,74</t>
+          <t>-5,31; 14,91</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-15,78; 2,6</t>
+          <t>-15,71; 1,99</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-58,12; -27,19</t>
+          <t>-39,93; -24,76</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-7,62</t>
+          <t>-9,42</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-7,12</t>
+          <t>-2,43</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-8,17</t>
+          <t>-5,92</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-4,06; 6,08</t>
+          <t>-4,4; 5,99</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,71; 9,81</t>
+          <t>-1,38; 9,81</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-13,24; -1,92</t>
+          <t>-14,8; -3,98</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,24; 9,31</t>
+          <t>0,3; 9,44</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,49; 9,55</t>
+          <t>0,06; 9,36</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-17,34; -0,99</t>
+          <t>-6,82; 1,95</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-0,79; 6,2</t>
+          <t>-0,66; 6,5</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,02; 8,09</t>
+          <t>1,28; 8,0</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-15,95; -3,68</t>
+          <t>-9,13; -2,57</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-21,08%</t>
+          <t>-26,06%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-29,85%</t>
+          <t>-10,2%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-27,26%</t>
+          <t>-19,75%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-10,54; 18,21</t>
+          <t>-11,3; 17,74</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-1,82; 28,89</t>
+          <t>-3,55; 30,19</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-33,82; -4,72</t>
+          <t>-37,66; -11,61</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,81; 41,73</t>
+          <t>1,19; 43,72</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1,24; 42,86</t>
+          <t>1,09; 44,64</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-66,3; -4,57</t>
+          <t>-25,76; 9,02</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-2,48; 21,98</t>
+          <t>-2,22; 23,26</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>3,21; 28,54</t>
+          <t>4,15; 28,98</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-52,45; -12,79</t>
+          <t>-29,19; -9,29</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-16,17</t>
+          <t>-15,44</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-9,78</t>
+          <t>-8,88</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-12,92</t>
+          <t>-12,03</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-8,1; 0,88</t>
+          <t>-8,43; 0,81</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-13,6; -5,1</t>
+          <t>-13,97; -5,21</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-20,53; -12,33</t>
+          <t>-19,95; -10,96</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-3,9; 4,01</t>
+          <t>-4,21; 3,61</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-7,09; 1,37</t>
+          <t>-6,94; 0,96</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-15,06; -6,42</t>
+          <t>-12,21; -5,48</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-4,68; 1,14</t>
+          <t>-4,84; 1,01</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-8,81; -3,09</t>
+          <t>-8,76; -2,98</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-16,24; -10,07</t>
+          <t>-14,72; -9,17</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-40,8%</t>
+          <t>-38,96%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-35,59%</t>
+          <t>-32,29%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-38,83%</t>
+          <t>-36,16%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-19,45; 2,36</t>
+          <t>-20,3; 2,1</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-32,84; -13,63</t>
+          <t>-33,19; -13,25</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-49,46; -32,16</t>
+          <t>-47,38; -29,0</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-13,18; 15,91</t>
+          <t>-14,2; 13,89</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-23,72; 5,28</t>
+          <t>-23,54; 3,08</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-51,13; -24,59</t>
+          <t>-41,27; -21,05</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-13,58; 3,55</t>
+          <t>-14,14; 3,11</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-25,45; -9,47</t>
+          <t>-25,4; -9,28</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-47,18; -31,45</t>
+          <t>-42,56; -29,03</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>-15,71</t>
+          <t>-14,3</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-6,73</t>
+          <t>-5,6</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-11,19</t>
+          <t>-9,92</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-5,63; -0,73</t>
+          <t>-5,54; -0,83</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-7,55; -2,72</t>
+          <t>-7,56; -2,86</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-21,58; -12,99</t>
+          <t>-16,54; -11,85</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,3; 4,59</t>
+          <t>0,08; 4,53</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 3,64</t>
+          <t>-0,5; 3,66</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-10,26; -4,42</t>
+          <t>-7,36; -3,7</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-1,8; 1,34</t>
+          <t>-1,9; 1,31</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-3,34; -0,16</t>
+          <t>-3,48; -0,19</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-14,18; -9,24</t>
+          <t>-11,4; -8,49</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>-39,43%</t>
+          <t>-35,88%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-27,43%</t>
+          <t>-22,82%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-34,89%</t>
+          <t>-30,93%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-13,55; -1,86</t>
+          <t>-13,46; -2,18</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-18,27; -7,06</t>
+          <t>-18,49; -7,39</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-53,17; -33,01</t>
+          <t>-40,67; -30,76</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1,3; 19,98</t>
+          <t>0,3; 18,97</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-2,5; 15,3</t>
+          <t>-1,88; 15,9</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-40,45; -18,68</t>
+          <t>-28,96; -15,76</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-5,51; 4,3</t>
+          <t>-5,79; 4,12</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-10,13; -0,49</t>
+          <t>-10,52; -0,56</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-43,95; -29,2</t>
+          <t>-34,75; -26,99</t>
         </is>
       </c>
     </row>
